--- a/results/-1Fold_links_baseline.xlsx
+++ b/results/-1Fold_links_baseline.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T6"/>
+  <dimension ref="A1:T4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -538,7 +538,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>coxtime</t>
+          <t>deepsurv</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -556,20 +556,20 @@
         <v>42</v>
       </c>
       <c r="G2" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="H2" t="n">
         <v>1</v>
       </c>
       <c r="I2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J2" t="n">
-        <v>256</v>
+        <v>1024</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>tanh</t>
+          <t>relu</t>
         </is>
       </c>
       <c r="L2" t="n">
@@ -584,22 +584,22 @@
         </is>
       </c>
       <c r="O2" t="n">
-        <v>0.9153470270206928</v>
+        <v>0.601140051603322</v>
       </c>
       <c r="P2" t="n">
-        <v>0.9031036548630116</v>
+        <v>0.6131706582187615</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.9681783865262719</v>
+        <v>0.6473032626496942</v>
       </c>
       <c r="R2" t="n">
-        <v>0.04366689494369953</v>
+        <v>0.1804936700420406</v>
       </c>
       <c r="S2" t="n">
-        <v>0.01706037302993061</v>
+        <v>0.01117441542611024</v>
       </c>
       <c r="T2" t="n">
-        <v>3.611749768257141</v>
+        <v>5.973867654800415</v>
       </c>
     </row>
     <row r="3">
@@ -610,7 +610,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>coxtime</t>
+          <t>deepsurv</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -625,23 +625,23 @@
         <v>100</v>
       </c>
       <c r="F3" t="n">
+        <v>42</v>
+      </c>
+      <c r="G3" t="n">
         <v>1</v>
-      </c>
-      <c r="G3" t="n">
-        <v>7</v>
       </c>
       <c r="H3" t="n">
         <v>1</v>
       </c>
       <c r="I3" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J3" t="n">
-        <v>256</v>
+        <v>1024</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>elu</t>
+          <t>relu</t>
         </is>
       </c>
       <c r="L3" t="n">
@@ -652,26 +652,26 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>gen</t>
+          <t>ph</t>
         </is>
       </c>
       <c r="O3" t="n">
-        <v>0.6354501031504598</v>
+        <v>0.6253843504529215</v>
       </c>
       <c r="P3" t="n">
-        <v>0.6649420225224335</v>
+        <v>0.6253837826240967</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.745865787857756</v>
+        <v>0.6684083358344647</v>
       </c>
       <c r="R3" t="n">
-        <v>0.06827796662008648</v>
+        <v>0.2101606385880458</v>
       </c>
       <c r="S3" t="n">
-        <v>0.05555624879281956</v>
+        <v>0.01058137253207614</v>
       </c>
       <c r="T3" t="n">
-        <v>4.834259867668152</v>
+        <v>5.505852580070496</v>
       </c>
     </row>
     <row r="4">
@@ -682,7 +682,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>coxtime</t>
+          <t>lassocox</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -694,26 +694,26 @@
         <v>-1</v>
       </c>
       <c r="E4" t="n">
-        <v>100</v>
+        <v>2</v>
       </c>
       <c r="F4" t="n">
-        <v>2026</v>
+        <v>42</v>
       </c>
       <c r="G4" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="H4" t="n">
         <v>1</v>
       </c>
       <c r="I4" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J4" t="n">
-        <v>256</v>
+        <v>1024</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>elu</t>
+          <t>relu</t>
         </is>
       </c>
       <c r="L4" t="n">
@@ -724,170 +724,26 @@
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>gen</t>
+          <t>ph</t>
         </is>
       </c>
       <c r="O4" t="n">
-        <v>0.6742545313986885</v>
+        <v>0.5326526716765356</v>
       </c>
       <c r="P4" t="n">
-        <v>0.6930566174874675</v>
+        <v>0.5326533295182888</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.7937615238170784</v>
+        <v>0.5356974217130989</v>
       </c>
       <c r="R4" t="n">
-        <v>0.05012720138971689</v>
+        <v>0.2247019313810688</v>
       </c>
       <c r="S4" t="n">
-        <v>0.05268960350995158</v>
+        <v>0.005996928535519538</v>
       </c>
       <c r="T4" t="n">
-        <v>4.696575582027435</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>links</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>coxtime</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>MLP</t>
-        </is>
-      </c>
-      <c r="D5" t="n">
-        <v>-1</v>
-      </c>
-      <c r="E5" t="n">
-        <v>100</v>
-      </c>
-      <c r="F5" t="n">
-        <v>13</v>
-      </c>
-      <c r="G5" t="n">
-        <v>7</v>
-      </c>
-      <c r="H5" t="n">
-        <v>1</v>
-      </c>
-      <c r="I5" t="n">
-        <v>4</v>
-      </c>
-      <c r="J5" t="n">
-        <v>256</v>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>elu</t>
-        </is>
-      </c>
-      <c r="L5" t="n">
-        <v>8000</v>
-      </c>
-      <c r="M5" t="n">
-        <v>2000</v>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>gen</t>
-        </is>
-      </c>
-      <c r="O5" t="n">
-        <v>0.7242969782368329</v>
-      </c>
-      <c r="P5" t="n">
-        <v>0.7524470385557832</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>0.8373860774006544</v>
-      </c>
-      <c r="R5" t="n">
-        <v>0.05425706114051688</v>
-      </c>
-      <c r="S5" t="n">
-        <v>0.04382127686368176</v>
-      </c>
-      <c r="T5" t="n">
-        <v>4.535015821456909</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>links</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>coxtime</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>MLP</t>
-        </is>
-      </c>
-      <c r="D6" t="n">
-        <v>-1</v>
-      </c>
-      <c r="E6" t="n">
-        <v>100</v>
-      </c>
-      <c r="F6" t="n">
-        <v>28</v>
-      </c>
-      <c r="G6" t="n">
-        <v>7</v>
-      </c>
-      <c r="H6" t="n">
-        <v>1</v>
-      </c>
-      <c r="I6" t="n">
-        <v>4</v>
-      </c>
-      <c r="J6" t="n">
-        <v>256</v>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>elu</t>
-        </is>
-      </c>
-      <c r="L6" t="n">
-        <v>8000</v>
-      </c>
-      <c r="M6" t="n">
-        <v>2000</v>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>gen</t>
-        </is>
-      </c>
-      <c r="O6" t="n">
-        <v>0.8913695169439706</v>
-      </c>
-      <c r="P6" t="n">
-        <v>0.8769572707237161</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>0.9539670989732095</v>
-      </c>
-      <c r="R6" t="n">
-        <v>0.04731282059149661</v>
-      </c>
-      <c r="S6" t="n">
-        <v>0.01884957571531357</v>
-      </c>
-      <c r="T6" t="n">
-        <v>3.772794961929321</v>
+        <v>4.396964192390442</v>
       </c>
     </row>
   </sheetData>
